--- a/DIM_TAMBUDGET.xlsx
+++ b/DIM_TAMBUDGET.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://freightways-my.sharepoint.com/personal/tuyet_pham_dxmail_co_nz/Documents/Desktop/PROJECTS/Sales Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="11_F25DC773A252ABDACC1048F1995C62D85BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E32FB871-BAE1-4CC1-9F8C-F20873477806}"/>
+  <xr:revisionPtr revIDLastSave="141" documentId="11_F25DC773A252ABDACC1048F1995C62D85BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AD992DB-8F61-4BD2-8464-2E4022A790EC}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="0" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="9">
   <si>
     <t>ID</t>
   </si>
@@ -87,12 +87,30 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -107,9 +125,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -136,8 +160,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FCC1715E-3E4E-43B0-8628-16C2D6541F7B}" name="DIM_TAMBUDGET" displayName="DIM_TAMBUDGET" ref="A1:E97" totalsRowShown="0">
-  <autoFilter ref="A1:E97" xr:uid="{FCC1715E-3E4E-43B0-8628-16C2D6541F7B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FCC1715E-3E4E-43B0-8628-16C2D6541F7B}" name="DIM_TAMBUDGET" displayName="DIM_TAMBUDGET" ref="A1:E121" totalsRowShown="0">
+  <autoFilter ref="A1:E121" xr:uid="{FCC1715E-3E4E-43B0-8628-16C2D6541F7B}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="2025"/>
+        <filter val="2026"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A8:E46">
     <sortCondition ref="B1:B49"/>
   </sortState>
@@ -415,9 +446,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E97"/>
+  <dimension ref="A1:E121"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -438,7 +470,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -455,7 +487,7 @@
         <v>582537.00799999991</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -472,7 +504,7 @@
         <v>654868.08649999998</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -489,7 +521,7 @@
         <v>797329.20099999988</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -506,7 +538,7 @@
         <v>552633.56949999998</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -523,7 +555,7 @@
         <v>657447.47899999993</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -540,109 +572,109 @@
         <v>799199.96349999995</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>2</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="3">
         <v>7</v>
       </c>
-      <c r="D8">
-        <v>2024</v>
-      </c>
-      <c r="E8" s="1">
+      <c r="D8" s="3">
+        <v>2024</v>
+      </c>
+      <c r="E8" s="2">
         <v>661564.65149999992</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>2</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="3">
         <v>8</v>
       </c>
-      <c r="D9">
-        <v>2024</v>
-      </c>
-      <c r="E9" s="1">
+      <c r="D9" s="3">
+        <v>2024</v>
+      </c>
+      <c r="E9" s="2">
         <v>694440.52949999995</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
         <v>2</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="3">
         <v>9</v>
       </c>
-      <c r="D10">
-        <v>2024</v>
-      </c>
-      <c r="E10" s="1">
+      <c r="D10" s="3">
+        <v>2024</v>
+      </c>
+      <c r="E10" s="2">
         <v>882902.32250000001</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
         <v>2</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="3">
         <v>10</v>
       </c>
-      <c r="D11">
-        <v>2024</v>
-      </c>
-      <c r="E11" s="1">
+      <c r="D11" s="3">
+        <v>2024</v>
+      </c>
+      <c r="E11" s="2">
         <v>620206.94849999994</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
         <v>2</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="3">
         <v>11</v>
       </c>
-      <c r="D12">
-        <v>2024</v>
-      </c>
-      <c r="E12" s="1">
+      <c r="D12" s="3">
+        <v>2024</v>
+      </c>
+      <c r="E12" s="2">
         <v>709368.89799999993</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
         <v>2</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="3">
         <v>12</v>
       </c>
-      <c r="D13">
-        <v>2024</v>
-      </c>
-      <c r="E13" s="1">
+      <c r="D13" s="3">
+        <v>2024</v>
+      </c>
+      <c r="E13" s="2">
         <v>728624.29099999985</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -659,7 +691,7 @@
         <v>542194.65149999992</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -676,7 +708,7 @@
         <v>521891.70049999998</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -693,7 +725,7 @@
         <v>700494.55499999993</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -710,7 +742,7 @@
         <v>563149.85950000002</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -727,7 +759,7 @@
         <v>575007.26799999992</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -744,109 +776,109 @@
         <v>728841.34199999995</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
         <v>3</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="3">
         <v>7</v>
       </c>
-      <c r="D20">
-        <v>2024</v>
-      </c>
-      <c r="E20" s="1">
+      <c r="D20" s="3">
+        <v>2024</v>
+      </c>
+      <c r="E20" s="2">
         <v>614557.21699999995</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
         <v>3</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="3">
         <v>8</v>
       </c>
-      <c r="D21">
-        <v>2024</v>
-      </c>
-      <c r="E21" s="1">
+      <c r="D21" s="3">
+        <v>2024</v>
+      </c>
+      <c r="E21" s="2">
         <v>713123.79749999999</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
         <v>3</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="3">
         <v>9</v>
       </c>
-      <c r="D22">
-        <v>2024</v>
-      </c>
-      <c r="E22" s="1">
+      <c r="D22" s="3">
+        <v>2024</v>
+      </c>
+      <c r="E22" s="2">
         <v>1143885.9099999999</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
         <v>3</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="3">
         <v>10</v>
       </c>
-      <c r="D23">
-        <v>2024</v>
-      </c>
-      <c r="E23" s="1">
+      <c r="D23" s="3">
+        <v>2024</v>
+      </c>
+      <c r="E23" s="2">
         <v>648287.42999999993</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
         <v>3</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="3">
         <v>11</v>
       </c>
-      <c r="D24">
-        <v>2024</v>
-      </c>
-      <c r="E24" s="1">
+      <c r="D24" s="3">
+        <v>2024</v>
+      </c>
+      <c r="E24" s="2">
         <v>656240.02499999991</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
         <v>3</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="3">
         <v>12</v>
       </c>
-      <c r="D25">
-        <v>2024</v>
-      </c>
-      <c r="E25" s="1">
+      <c r="D25" s="3">
+        <v>2024</v>
+      </c>
+      <c r="E25" s="2">
         <v>830959.01899999997</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -863,7 +895,7 @@
         <v>500377.85699999996</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -880,7 +912,7 @@
         <v>651203.87599999993</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -897,7 +929,7 @@
         <v>869339.65949999995</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -914,7 +946,7 @@
         <v>569400.58100000001</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -931,7 +963,7 @@
         <v>699794.40049999999</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -948,109 +980,109 @@
         <v>834302.74749999994</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
         <v>4</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="4">
         <v>7</v>
       </c>
-      <c r="D32">
-        <v>2024</v>
-      </c>
-      <c r="E32" s="1">
+      <c r="D32" s="4">
+        <v>2024</v>
+      </c>
+      <c r="E32" s="5">
         <v>687764.36549999996</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
         <v>4</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="4">
         <v>8</v>
       </c>
-      <c r="D33">
-        <v>2024</v>
-      </c>
-      <c r="E33" s="1">
+      <c r="D33" s="4">
+        <v>2024</v>
+      </c>
+      <c r="E33" s="5">
         <v>770244.99899999995</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
         <v>4</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="4">
         <v>9</v>
       </c>
-      <c r="D34">
-        <v>2024</v>
-      </c>
-      <c r="E34" s="1">
+      <c r="D34" s="4">
+        <v>2024</v>
+      </c>
+      <c r="E34" s="5">
         <v>761492.83200000005</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
         <v>4</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="4">
         <v>10</v>
       </c>
-      <c r="D35">
-        <v>2024</v>
-      </c>
-      <c r="E35" s="1">
+      <c r="D35" s="4">
+        <v>2024</v>
+      </c>
+      <c r="E35" s="5">
         <v>679340.73049999983</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
         <v>4</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="4">
         <v>11</v>
       </c>
-      <c r="D36">
-        <v>2024</v>
-      </c>
-      <c r="E36" s="1">
+      <c r="D36" s="4">
+        <v>2024</v>
+      </c>
+      <c r="E36" s="5">
         <v>757416.07050000003</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
         <v>4</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="4">
         <v>12</v>
       </c>
-      <c r="D37">
-        <v>2024</v>
-      </c>
-      <c r="E37" s="1">
+      <c r="D37" s="4">
+        <v>2024</v>
+      </c>
+      <c r="E37" s="5">
         <v>804767.723</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1067,7 +1099,7 @@
         <v>414797.9045</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1084,7 +1116,7 @@
         <v>531217.09649999999</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1101,7 +1133,7 @@
         <v>661341.67799999996</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1118,7 +1150,7 @@
         <v>588442.62599999993</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1135,7 +1167,7 @@
         <v>528540.40249999997</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1152,105 +1184,105 @@
         <v>693135.8544999999</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
         <v>5</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="6">
         <v>7</v>
       </c>
-      <c r="D44">
-        <v>2024</v>
-      </c>
-      <c r="E44" s="1">
+      <c r="D44" s="6">
+        <v>2024</v>
+      </c>
+      <c r="E44" s="7">
         <v>518672.53999999992</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
         <v>5</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="6">
         <v>8</v>
       </c>
-      <c r="D45">
-        <v>2024</v>
-      </c>
-      <c r="E45" s="1">
+      <c r="D45" s="6">
+        <v>2024</v>
+      </c>
+      <c r="E45" s="7">
         <v>679348.20549999992</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
         <v>5</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="6">
         <v>9</v>
       </c>
-      <c r="D46">
-        <v>2024</v>
-      </c>
-      <c r="E46" s="1">
+      <c r="D46" s="6">
+        <v>2024</v>
+      </c>
+      <c r="E46" s="7">
         <v>765394.09199999995</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="s">
         <v>5</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="6">
         <v>10</v>
       </c>
-      <c r="D47">
-        <v>2024</v>
-      </c>
-      <c r="E47" s="1">
+      <c r="D47" s="6">
+        <v>2024</v>
+      </c>
+      <c r="E47" s="7">
         <v>658911.33699999994</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
         <v>5</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="6">
         <v>11</v>
       </c>
-      <c r="D48">
-        <v>2024</v>
-      </c>
-      <c r="E48" s="1">
+      <c r="D48" s="6">
+        <v>2024</v>
+      </c>
+      <c r="E48" s="7">
         <v>697444.65149999992</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
         <v>5</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="6">
         <v>12</v>
       </c>
-      <c r="D49">
-        <v>2024</v>
-      </c>
-      <c r="E49" s="1">
+      <c r="D49" s="6">
+        <v>2024</v>
+      </c>
+      <c r="E49" s="7">
         <v>837874.02649999992</v>
       </c>
     </row>
@@ -1261,13 +1293,13 @@
       <c r="B50" t="s">
         <v>2</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="3">
         <v>1</v>
       </c>
-      <c r="D50">
-        <v>2025</v>
-      </c>
-      <c r="E50" s="1">
+      <c r="D50" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E50" s="2">
         <v>546467.35</v>
       </c>
     </row>
@@ -1278,13 +1310,13 @@
       <c r="B51" t="s">
         <v>2</v>
       </c>
-      <c r="C51">
-        <v>2</v>
-      </c>
-      <c r="D51">
-        <v>2025</v>
-      </c>
-      <c r="E51" s="1">
+      <c r="C51" s="3">
+        <v>2</v>
+      </c>
+      <c r="D51" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E51" s="2">
         <v>648087.1</v>
       </c>
     </row>
@@ -1295,13 +1327,13 @@
       <c r="B52" t="s">
         <v>2</v>
       </c>
-      <c r="C52">
-        <v>3</v>
-      </c>
-      <c r="D52">
-        <v>2025</v>
-      </c>
-      <c r="E52" s="1">
+      <c r="C52" s="3">
+        <v>3</v>
+      </c>
+      <c r="D52" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E52" s="2">
         <v>741740.8</v>
       </c>
     </row>
@@ -1312,13 +1344,13 @@
       <c r="B53" t="s">
         <v>2</v>
       </c>
-      <c r="C53">
-        <v>4</v>
-      </c>
-      <c r="D53">
-        <v>2025</v>
-      </c>
-      <c r="E53" s="1">
+      <c r="C53" s="3">
+        <v>4</v>
+      </c>
+      <c r="D53" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E53" s="2">
         <v>607427.69999999995</v>
       </c>
     </row>
@@ -1329,13 +1361,13 @@
       <c r="B54" t="s">
         <v>2</v>
       </c>
-      <c r="C54">
-        <v>5</v>
-      </c>
-      <c r="D54">
-        <v>2025</v>
-      </c>
-      <c r="E54" s="1">
+      <c r="C54" s="3">
+        <v>5</v>
+      </c>
+      <c r="D54" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E54" s="2">
         <v>640505.15</v>
       </c>
     </row>
@@ -1346,13 +1378,13 @@
       <c r="B55" t="s">
         <v>2</v>
       </c>
-      <c r="C55">
+      <c r="C55" s="3">
         <v>6</v>
       </c>
-      <c r="D55">
-        <v>2025</v>
-      </c>
-      <c r="E55" s="1">
+      <c r="D55" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E55" s="2">
         <v>720247.3</v>
       </c>
     </row>
@@ -1370,7 +1402,7 @@
         <v>2025</v>
       </c>
       <c r="E56" s="1">
-        <v>542840.25</v>
+        <v>519238.50000000006</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -1387,7 +1419,7 @@
         <v>2025</v>
       </c>
       <c r="E57" s="1">
-        <v>608399.44999999995</v>
+        <v>581947.30000000005</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -1404,7 +1436,7 @@
         <v>2025</v>
       </c>
       <c r="E58" s="1">
-        <v>524134.35</v>
+        <v>501345.9</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -1421,7 +1453,7 @@
         <v>2025</v>
       </c>
       <c r="E59" s="1">
-        <v>539366.1</v>
+        <v>515915.4</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -1438,7 +1470,7 @@
         <v>2025</v>
       </c>
       <c r="E60" s="1">
-        <v>689172</v>
+        <v>659208</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -1455,7 +1487,7 @@
         <v>2025</v>
       </c>
       <c r="E61" s="1">
-        <v>461187.95</v>
+        <v>441136.30000000005</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -1465,13 +1497,13 @@
       <c r="B62" t="s">
         <v>3</v>
       </c>
-      <c r="C62">
+      <c r="C62" s="3">
         <v>1</v>
       </c>
-      <c r="D62">
-        <v>2025</v>
-      </c>
-      <c r="E62" s="1">
+      <c r="D62" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E62" s="2">
         <v>460018.4</v>
       </c>
     </row>
@@ -1482,13 +1514,13 @@
       <c r="B63" t="s">
         <v>3</v>
       </c>
-      <c r="C63">
-        <v>2</v>
-      </c>
-      <c r="D63">
-        <v>2025</v>
-      </c>
-      <c r="E63" s="1">
+      <c r="C63" s="3">
+        <v>2</v>
+      </c>
+      <c r="D63" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E63" s="2">
         <v>701240.1</v>
       </c>
     </row>
@@ -1499,13 +1531,13 @@
       <c r="B64" t="s">
         <v>3</v>
       </c>
-      <c r="C64">
-        <v>3</v>
-      </c>
-      <c r="D64">
-        <v>2025</v>
-      </c>
-      <c r="E64" s="1">
+      <c r="C64" s="3">
+        <v>3</v>
+      </c>
+      <c r="D64" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E64" s="2">
         <v>761615.1</v>
       </c>
     </row>
@@ -1516,13 +1548,13 @@
       <c r="B65" t="s">
         <v>3</v>
       </c>
-      <c r="C65">
-        <v>4</v>
-      </c>
-      <c r="D65">
-        <v>2025</v>
-      </c>
-      <c r="E65" s="1">
+      <c r="C65" s="3">
+        <v>4</v>
+      </c>
+      <c r="D65" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E65" s="2">
         <v>562320.1</v>
       </c>
     </row>
@@ -1533,13 +1565,13 @@
       <c r="B66" t="s">
         <v>3</v>
       </c>
-      <c r="C66">
-        <v>5</v>
-      </c>
-      <c r="D66">
-        <v>2025</v>
-      </c>
-      <c r="E66" s="1">
+      <c r="C66" s="3">
+        <v>5</v>
+      </c>
+      <c r="D66" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E66" s="2">
         <v>729120.7</v>
       </c>
     </row>
@@ -1550,13 +1582,13 @@
       <c r="B67" t="s">
         <v>3</v>
       </c>
-      <c r="C67">
+      <c r="C67" s="3">
         <v>6</v>
       </c>
-      <c r="D67">
-        <v>2025</v>
-      </c>
-      <c r="E67" s="1">
+      <c r="D67" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E67" s="2">
         <v>872906.35</v>
       </c>
     </row>
@@ -1574,7 +1606,7 @@
         <v>2025</v>
       </c>
       <c r="E68" s="1">
-        <v>652349</v>
+        <v>623986</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -1591,7 +1623,7 @@
         <v>2025</v>
       </c>
       <c r="E69" s="1">
-        <v>869364.35</v>
+        <v>831565.9</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -1608,7 +1640,7 @@
         <v>2025</v>
       </c>
       <c r="E70" s="1">
-        <v>896605.55</v>
+        <v>857622.70000000007</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -1625,7 +1657,7 @@
         <v>2025</v>
       </c>
       <c r="E71" s="1">
-        <v>664905.85</v>
+        <v>635996.9</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -1642,7 +1674,7 @@
         <v>2025</v>
       </c>
       <c r="E72" s="1">
-        <v>859504.25</v>
+        <v>822134.50000000012</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -1659,7 +1691,7 @@
         <v>2025</v>
       </c>
       <c r="E73" s="1">
-        <v>691767.55</v>
+        <v>661690.70000000007</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -1669,13 +1701,13 @@
       <c r="B74" t="s">
         <v>4</v>
       </c>
-      <c r="C74">
+      <c r="C74" s="3">
         <v>1</v>
       </c>
-      <c r="D74">
-        <v>2025</v>
-      </c>
-      <c r="E74" s="1">
+      <c r="D74" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E74" s="2">
         <v>483127.65</v>
       </c>
     </row>
@@ -1686,13 +1718,13 @@
       <c r="B75" t="s">
         <v>4</v>
       </c>
-      <c r="C75">
-        <v>2</v>
-      </c>
-      <c r="D75">
-        <v>2025</v>
-      </c>
-      <c r="E75" s="1">
+      <c r="C75" s="3">
+        <v>2</v>
+      </c>
+      <c r="D75" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E75" s="2">
         <v>707742.2</v>
       </c>
     </row>
@@ -1703,13 +1735,13 @@
       <c r="B76" t="s">
         <v>4</v>
       </c>
-      <c r="C76">
-        <v>3</v>
-      </c>
-      <c r="D76">
-        <v>2025</v>
-      </c>
-      <c r="E76" s="1">
+      <c r="C76" s="3">
+        <v>3</v>
+      </c>
+      <c r="D76" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E76" s="2">
         <v>924192.9</v>
       </c>
     </row>
@@ -1720,13 +1752,13 @@
       <c r="B77" t="s">
         <v>4</v>
       </c>
-      <c r="C77">
-        <v>4</v>
-      </c>
-      <c r="D77">
-        <v>2025</v>
-      </c>
-      <c r="E77" s="1">
+      <c r="C77" s="3">
+        <v>4</v>
+      </c>
+      <c r="D77" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E77" s="2">
         <v>648338.94999999995</v>
       </c>
     </row>
@@ -1737,13 +1769,13 @@
       <c r="B78" t="s">
         <v>4</v>
       </c>
-      <c r="C78">
-        <v>5</v>
-      </c>
-      <c r="D78">
-        <v>2025</v>
-      </c>
-      <c r="E78" s="1">
+      <c r="C78" s="3">
+        <v>5</v>
+      </c>
+      <c r="D78" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E78" s="2">
         <v>709702.95</v>
       </c>
     </row>
@@ -1754,13 +1786,13 @@
       <c r="B79" t="s">
         <v>4</v>
       </c>
-      <c r="C79">
+      <c r="C79" s="3">
         <v>6</v>
       </c>
-      <c r="D79">
-        <v>2025</v>
-      </c>
-      <c r="E79" s="1">
+      <c r="D79" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E79" s="2">
         <v>819977.6</v>
       </c>
     </row>
@@ -1778,7 +1810,7 @@
         <v>2025</v>
       </c>
       <c r="E80" s="1">
-        <v>627557.30000000005</v>
+        <v>600272.20000000007</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -1795,7 +1827,7 @@
         <v>2025</v>
       </c>
       <c r="E81" s="1">
-        <v>833225.6</v>
+        <v>796998.4</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -1812,7 +1844,7 @@
         <v>2025</v>
       </c>
       <c r="E82" s="1">
-        <v>654592.65</v>
+        <v>626132.10000000009</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -1829,7 +1861,7 @@
         <v>2025</v>
       </c>
       <c r="E83" s="1">
-        <v>618613.75</v>
+        <v>591717.5</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -1846,7 +1878,7 @@
         <v>2025</v>
       </c>
       <c r="E84" s="1">
-        <v>826988</v>
+        <v>791032.00000000012</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -1863,7 +1895,7 @@
         <v>2025</v>
       </c>
       <c r="E85" s="1">
-        <v>691914.75</v>
+        <v>661831.5</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -1873,13 +1905,13 @@
       <c r="B86" t="s">
         <v>5</v>
       </c>
-      <c r="C86">
+      <c r="C86" s="3">
         <v>1</v>
       </c>
-      <c r="D86">
-        <v>2025</v>
-      </c>
-      <c r="E86" s="1">
+      <c r="D86" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E86" s="2">
         <v>444077.1</v>
       </c>
     </row>
@@ -1890,13 +1922,13 @@
       <c r="B87" t="s">
         <v>5</v>
       </c>
-      <c r="C87">
-        <v>2</v>
-      </c>
-      <c r="D87">
-        <v>2025</v>
-      </c>
-      <c r="E87" s="1">
+      <c r="C87" s="3">
+        <v>2</v>
+      </c>
+      <c r="D87" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E87" s="2">
         <v>565701.1</v>
       </c>
     </row>
@@ -1907,13 +1939,13 @@
       <c r="B88" t="s">
         <v>5</v>
       </c>
-      <c r="C88">
-        <v>3</v>
-      </c>
-      <c r="D88">
-        <v>2025</v>
-      </c>
-      <c r="E88" s="1">
+      <c r="C88" s="3">
+        <v>3</v>
+      </c>
+      <c r="D88" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E88" s="2">
         <v>699833.65</v>
       </c>
     </row>
@@ -1924,13 +1956,13 @@
       <c r="B89" t="s">
         <v>5</v>
       </c>
-      <c r="C89">
-        <v>4</v>
-      </c>
-      <c r="D89">
-        <v>2025</v>
-      </c>
-      <c r="E89" s="1">
+      <c r="C89" s="3">
+        <v>4</v>
+      </c>
+      <c r="D89" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E89" s="2">
         <v>578230.35</v>
       </c>
     </row>
@@ -1941,13 +1973,13 @@
       <c r="B90" t="s">
         <v>5</v>
       </c>
-      <c r="C90">
-        <v>5</v>
-      </c>
-      <c r="D90">
-        <v>2025</v>
-      </c>
-      <c r="E90" s="1">
+      <c r="C90" s="3">
+        <v>5</v>
+      </c>
+      <c r="D90" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E90" s="2">
         <v>649040.44999999995</v>
       </c>
     </row>
@@ -1958,13 +1990,13 @@
       <c r="B91" t="s">
         <v>5</v>
       </c>
-      <c r="C91">
+      <c r="C91" s="3">
         <v>6</v>
       </c>
-      <c r="D91">
-        <v>2025</v>
-      </c>
-      <c r="E91" s="1">
+      <c r="D91" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E91" s="2">
         <v>737522.6</v>
       </c>
     </row>
@@ -1982,7 +2014,7 @@
         <v>2025</v>
       </c>
       <c r="E92" s="1">
-        <v>588297.44999999995</v>
+        <v>562719.30000000005</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -1999,7 +2031,7 @@
         <v>2025</v>
       </c>
       <c r="E93" s="1">
-        <v>815517.9</v>
+        <v>780060.60000000009</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -2016,7 +2048,7 @@
         <v>2025</v>
       </c>
       <c r="E94" s="1">
-        <v>633692.55000000005</v>
+        <v>606140.70000000007</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -2033,7 +2065,7 @@
         <v>2025</v>
       </c>
       <c r="E95" s="1">
-        <v>630599.05000000005</v>
+        <v>603181.70000000007</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -2050,7 +2082,7 @@
         <v>2025</v>
       </c>
       <c r="E96" s="1">
-        <v>740374.6</v>
+        <v>708184.4</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -2067,7 +2099,415 @@
         <v>2025</v>
       </c>
       <c r="E97" s="1">
-        <v>754549.5</v>
+        <v>721743.00000000012</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>2</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
+      <c r="D98">
+        <v>2026</v>
+      </c>
+      <c r="E98" s="1">
+        <v>447132.4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>2</v>
+      </c>
+      <c r="C99">
+        <v>2</v>
+      </c>
+      <c r="D99">
+        <v>2026</v>
+      </c>
+      <c r="E99" s="1">
+        <v>583671</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>2</v>
+      </c>
+      <c r="C100">
+        <v>3</v>
+      </c>
+      <c r="D100">
+        <v>2026</v>
+      </c>
+      <c r="E100" s="1">
+        <v>543246</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>2</v>
+      </c>
+      <c r="C101">
+        <v>4</v>
+      </c>
+      <c r="D101">
+        <v>2026</v>
+      </c>
+      <c r="E101" s="1">
+        <v>420537.7</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C102">
+        <v>5</v>
+      </c>
+      <c r="D102">
+        <v>2026</v>
+      </c>
+      <c r="E102" s="1">
+        <v>610426.30000000005</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
+        <v>2</v>
+      </c>
+      <c r="C103">
+        <v>6</v>
+      </c>
+      <c r="D103">
+        <v>2026</v>
+      </c>
+      <c r="E103" s="1">
+        <v>430988.80000000005</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>3</v>
+      </c>
+      <c r="C104">
+        <v>1</v>
+      </c>
+      <c r="D104">
+        <v>2026</v>
+      </c>
+      <c r="E104" s="1">
+        <v>468160.00000000006</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" t="s">
+        <v>3</v>
+      </c>
+      <c r="C105">
+        <v>2</v>
+      </c>
+      <c r="D105">
+        <v>2026</v>
+      </c>
+      <c r="E105" s="1">
+        <v>710494.4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>3</v>
+      </c>
+      <c r="C106">
+        <v>3</v>
+      </c>
+      <c r="D106">
+        <v>2026</v>
+      </c>
+      <c r="E106" s="1">
+        <v>734202.70000000007</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
+        <v>3</v>
+      </c>
+      <c r="C107">
+        <v>4</v>
+      </c>
+      <c r="D107">
+        <v>2026</v>
+      </c>
+      <c r="E107" s="1">
+        <v>533989.5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" t="s">
+        <v>3</v>
+      </c>
+      <c r="C108">
+        <v>5</v>
+      </c>
+      <c r="D108">
+        <v>2026</v>
+      </c>
+      <c r="E108" s="1">
+        <v>783138.4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" t="s">
+        <v>3</v>
+      </c>
+      <c r="C109">
+        <v>6</v>
+      </c>
+      <c r="D109">
+        <v>2026</v>
+      </c>
+      <c r="E109" s="1">
+        <v>632283.30000000005</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" t="s">
+        <v>4</v>
+      </c>
+      <c r="C110">
+        <v>1</v>
+      </c>
+      <c r="D110">
+        <v>2026</v>
+      </c>
+      <c r="E110" s="1">
+        <v>420468.4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" t="s">
+        <v>4</v>
+      </c>
+      <c r="C111">
+        <v>2</v>
+      </c>
+      <c r="D111">
+        <v>2026</v>
+      </c>
+      <c r="E111" s="1">
+        <v>768489.70000000007</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" t="s">
+        <v>4</v>
+      </c>
+      <c r="C112">
+        <v>3</v>
+      </c>
+      <c r="D112">
+        <v>2026</v>
+      </c>
+      <c r="E112" s="1">
+        <v>707430.9</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113" t="s">
+        <v>4</v>
+      </c>
+      <c r="C113">
+        <v>4</v>
+      </c>
+      <c r="D113">
+        <v>2026</v>
+      </c>
+      <c r="E113" s="1">
+        <v>548621.70000000007</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" t="s">
+        <v>4</v>
+      </c>
+      <c r="C114">
+        <v>5</v>
+      </c>
+      <c r="D114">
+        <v>2026</v>
+      </c>
+      <c r="E114" s="1">
+        <v>628012</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" t="s">
+        <v>4</v>
+      </c>
+      <c r="C115">
+        <v>6</v>
+      </c>
+      <c r="D115">
+        <v>2026</v>
+      </c>
+      <c r="E115" s="1">
+        <v>654494.5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116" t="s">
+        <v>5</v>
+      </c>
+      <c r="C116">
+        <v>1</v>
+      </c>
+      <c r="D116">
+        <v>2026</v>
+      </c>
+      <c r="E116" s="1">
+        <v>408622.50000000006</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" t="s">
+        <v>5</v>
+      </c>
+      <c r="C117">
+        <v>2</v>
+      </c>
+      <c r="D117">
+        <v>2026</v>
+      </c>
+      <c r="E117" s="1">
+        <v>710213.9</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118" t="s">
+        <v>5</v>
+      </c>
+      <c r="C118">
+        <v>3</v>
+      </c>
+      <c r="D118">
+        <v>2026</v>
+      </c>
+      <c r="E118" s="1">
+        <v>534640.70000000007</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119" t="s">
+        <v>5</v>
+      </c>
+      <c r="C119">
+        <v>4</v>
+      </c>
+      <c r="D119">
+        <v>2026</v>
+      </c>
+      <c r="E119" s="1">
+        <v>565877.4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120" t="s">
+        <v>5</v>
+      </c>
+      <c r="C120">
+        <v>5</v>
+      </c>
+      <c r="D120">
+        <v>2026</v>
+      </c>
+      <c r="E120" s="1">
+        <v>699802.4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121" t="s">
+        <v>5</v>
+      </c>
+      <c r="C121">
+        <v>6</v>
+      </c>
+      <c r="D121">
+        <v>2026</v>
+      </c>
+      <c r="E121" s="1">
+        <v>649240.9</v>
       </c>
     </row>
   </sheetData>

--- a/DIM_TAMBUDGET.xlsx
+++ b/DIM_TAMBUDGET.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://freightways-my.sharepoint.com/personal/tuyet_pham_dxmail_co_nz/Documents/Desktop/PROJECTS/Sales Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="141" documentId="11_F25DC773A252ABDACC1048F1995C62D85BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AD992DB-8F61-4BD2-8464-2E4022A790EC}"/>
+  <xr:revisionPtr revIDLastSave="169" documentId="11_F25DC773A252ABDACC1048F1995C62D85BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{997F5A7B-FA68-456A-A379-F2E4BB76B21F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -87,7 +87,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -96,19 +96,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -125,15 +113,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -155,20 +139,9 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FCC1715E-3E4E-43B0-8628-16C2D6541F7B}" name="DIM_TAMBUDGET" displayName="DIM_TAMBUDGET" ref="A1:E121" totalsRowShown="0">
-  <autoFilter ref="A1:E121" xr:uid="{FCC1715E-3E4E-43B0-8628-16C2D6541F7B}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="2025"/>
-        <filter val="2026"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:E121" xr:uid="{FCC1715E-3E4E-43B0-8628-16C2D6541F7B}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A8:E46">
     <sortCondition ref="B1:B49"/>
   </sortState>
@@ -470,7 +443,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -487,7 +460,7 @@
         <v>582537.00799999991</v>
       </c>
     </row>
-    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -504,7 +477,7 @@
         <v>654868.08649999998</v>
       </c>
     </row>
-    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -521,7 +494,7 @@
         <v>797329.20099999988</v>
       </c>
     </row>
-    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -538,7 +511,7 @@
         <v>552633.56949999998</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -555,7 +528,7 @@
         <v>657447.47899999993</v>
       </c>
     </row>
-    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -572,109 +545,109 @@
         <v>799199.96349999995</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8">
         <v>7</v>
       </c>
-      <c r="D8" s="3">
-        <v>2024</v>
-      </c>
-      <c r="E8" s="2">
+      <c r="D8">
+        <v>2024</v>
+      </c>
+      <c r="E8" s="1">
         <v>661564.65149999992</v>
       </c>
     </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9">
         <v>8</v>
       </c>
-      <c r="D9" s="3">
-        <v>2024</v>
-      </c>
-      <c r="E9" s="2">
+      <c r="D9">
+        <v>2024</v>
+      </c>
+      <c r="E9" s="1">
         <v>694440.52949999995</v>
       </c>
     </row>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10">
         <v>9</v>
       </c>
-      <c r="D10" s="3">
-        <v>2024</v>
-      </c>
-      <c r="E10" s="2">
+      <c r="D10">
+        <v>2024</v>
+      </c>
+      <c r="E10" s="1">
         <v>882902.32250000001</v>
       </c>
     </row>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11">
         <v>10</v>
       </c>
-      <c r="D11" s="3">
-        <v>2024</v>
-      </c>
-      <c r="E11" s="2">
+      <c r="D11">
+        <v>2024</v>
+      </c>
+      <c r="E11" s="1">
         <v>620206.94849999994</v>
       </c>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12">
         <v>11</v>
       </c>
-      <c r="D12" s="3">
-        <v>2024</v>
-      </c>
-      <c r="E12" s="2">
+      <c r="D12">
+        <v>2024</v>
+      </c>
+      <c r="E12" s="1">
         <v>709368.89799999993</v>
       </c>
     </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13">
         <v>12</v>
       </c>
-      <c r="D13" s="3">
-        <v>2024</v>
-      </c>
-      <c r="E13" s="2">
+      <c r="D13">
+        <v>2024</v>
+      </c>
+      <c r="E13" s="1">
         <v>728624.29099999985</v>
       </c>
     </row>
-    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -691,7 +664,7 @@
         <v>542194.65149999992</v>
       </c>
     </row>
-    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -708,7 +681,7 @@
         <v>521891.70049999998</v>
       </c>
     </row>
-    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -725,7 +698,7 @@
         <v>700494.55499999993</v>
       </c>
     </row>
-    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -742,7 +715,7 @@
         <v>563149.85950000002</v>
       </c>
     </row>
-    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -759,7 +732,7 @@
         <v>575007.26799999992</v>
       </c>
     </row>
-    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -776,109 +749,109 @@
         <v>728841.34199999995</v>
       </c>
     </row>
-    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
         <v>3</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20">
         <v>7</v>
       </c>
-      <c r="D20" s="3">
-        <v>2024</v>
-      </c>
-      <c r="E20" s="2">
+      <c r="D20">
+        <v>2024</v>
+      </c>
+      <c r="E20" s="1">
         <v>614557.21699999995</v>
       </c>
     </row>
-    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
         <v>3</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21">
         <v>8</v>
       </c>
-      <c r="D21" s="3">
-        <v>2024</v>
-      </c>
-      <c r="E21" s="2">
+      <c r="D21">
+        <v>2024</v>
+      </c>
+      <c r="E21" s="1">
         <v>713123.79749999999</v>
       </c>
     </row>
-    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
         <v>3</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22">
         <v>9</v>
       </c>
-      <c r="D22" s="3">
-        <v>2024</v>
-      </c>
-      <c r="E22" s="2">
+      <c r="D22">
+        <v>2024</v>
+      </c>
+      <c r="E22" s="1">
         <v>1143885.9099999999</v>
       </c>
     </row>
-    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
         <v>3</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23">
         <v>10</v>
       </c>
-      <c r="D23" s="3">
-        <v>2024</v>
-      </c>
-      <c r="E23" s="2">
+      <c r="D23">
+        <v>2024</v>
+      </c>
+      <c r="E23" s="1">
         <v>648287.42999999993</v>
       </c>
     </row>
-    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24">
         <v>11</v>
       </c>
-      <c r="D24" s="3">
-        <v>2024</v>
-      </c>
-      <c r="E24" s="2">
+      <c r="D24">
+        <v>2024</v>
+      </c>
+      <c r="E24" s="1">
         <v>656240.02499999991</v>
       </c>
     </row>
-    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
         <v>3</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25">
         <v>12</v>
       </c>
-      <c r="D25" s="3">
-        <v>2024</v>
-      </c>
-      <c r="E25" s="2">
+      <c r="D25">
+        <v>2024</v>
+      </c>
+      <c r="E25" s="1">
         <v>830959.01899999997</v>
       </c>
     </row>
-    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -895,7 +868,7 @@
         <v>500377.85699999996</v>
       </c>
     </row>
-    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -912,7 +885,7 @@
         <v>651203.87599999993</v>
       </c>
     </row>
-    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -929,7 +902,7 @@
         <v>869339.65949999995</v>
       </c>
     </row>
-    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -946,7 +919,7 @@
         <v>569400.58100000001</v>
       </c>
     </row>
-    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -963,7 +936,7 @@
         <v>699794.40049999999</v>
       </c>
     </row>
-    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -980,109 +953,109 @@
         <v>834302.74749999994</v>
       </c>
     </row>
-    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
         <v>4</v>
       </c>
-      <c r="C32" s="4">
+      <c r="C32">
         <v>7</v>
       </c>
-      <c r="D32" s="4">
-        <v>2024</v>
-      </c>
-      <c r="E32" s="5">
+      <c r="D32">
+        <v>2024</v>
+      </c>
+      <c r="E32" s="1">
         <v>687764.36549999996</v>
       </c>
     </row>
-    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
         <v>4</v>
       </c>
-      <c r="C33" s="4">
+      <c r="C33">
         <v>8</v>
       </c>
-      <c r="D33" s="4">
-        <v>2024</v>
-      </c>
-      <c r="E33" s="5">
+      <c r="D33">
+        <v>2024</v>
+      </c>
+      <c r="E33" s="1">
         <v>770244.99899999995</v>
       </c>
     </row>
-    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C34">
         <v>9</v>
       </c>
-      <c r="D34" s="4">
-        <v>2024</v>
-      </c>
-      <c r="E34" s="5">
+      <c r="D34">
+        <v>2024</v>
+      </c>
+      <c r="E34" s="1">
         <v>761492.83200000005</v>
       </c>
     </row>
-    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
         <v>4</v>
       </c>
-      <c r="C35" s="4">
+      <c r="C35">
         <v>10</v>
       </c>
-      <c r="D35" s="4">
-        <v>2024</v>
-      </c>
-      <c r="E35" s="5">
+      <c r="D35">
+        <v>2024</v>
+      </c>
+      <c r="E35" s="1">
         <v>679340.73049999983</v>
       </c>
     </row>
-    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
         <v>4</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C36">
         <v>11</v>
       </c>
-      <c r="D36" s="4">
-        <v>2024</v>
-      </c>
-      <c r="E36" s="5">
+      <c r="D36">
+        <v>2024</v>
+      </c>
+      <c r="E36" s="1">
         <v>757416.07050000003</v>
       </c>
     </row>
-    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
         <v>4</v>
       </c>
-      <c r="C37" s="4">
+      <c r="C37">
         <v>12</v>
       </c>
-      <c r="D37" s="4">
-        <v>2024</v>
-      </c>
-      <c r="E37" s="5">
+      <c r="D37">
+        <v>2024</v>
+      </c>
+      <c r="E37" s="1">
         <v>804767.723</v>
       </c>
     </row>
-    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1099,7 +1072,7 @@
         <v>414797.9045</v>
       </c>
     </row>
-    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1116,7 +1089,7 @@
         <v>531217.09649999999</v>
       </c>
     </row>
-    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1133,7 +1106,7 @@
         <v>661341.67799999996</v>
       </c>
     </row>
-    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1150,7 +1123,7 @@
         <v>588442.62599999993</v>
       </c>
     </row>
-    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1167,7 +1140,7 @@
         <v>528540.40249999997</v>
       </c>
     </row>
-    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1184,105 +1157,105 @@
         <v>693135.8544999999</v>
       </c>
     </row>
-    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="6">
+      <c r="C44">
         <v>7</v>
       </c>
-      <c r="D44" s="6">
-        <v>2024</v>
-      </c>
-      <c r="E44" s="7">
+      <c r="D44">
+        <v>2024</v>
+      </c>
+      <c r="E44" s="1">
         <v>518672.53999999992</v>
       </c>
     </row>
-    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
         <v>5</v>
       </c>
-      <c r="C45" s="6">
+      <c r="C45">
         <v>8</v>
       </c>
-      <c r="D45" s="6">
-        <v>2024</v>
-      </c>
-      <c r="E45" s="7">
+      <c r="D45">
+        <v>2024</v>
+      </c>
+      <c r="E45" s="1">
         <v>679348.20549999992</v>
       </c>
     </row>
-    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="6">
+      <c r="C46">
         <v>9</v>
       </c>
-      <c r="D46" s="6">
-        <v>2024</v>
-      </c>
-      <c r="E46" s="7">
+      <c r="D46">
+        <v>2024</v>
+      </c>
+      <c r="E46" s="1">
         <v>765394.09199999995</v>
       </c>
     </row>
-    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="s">
         <v>5</v>
       </c>
-      <c r="C47" s="6">
+      <c r="C47">
         <v>10</v>
       </c>
-      <c r="D47" s="6">
-        <v>2024</v>
-      </c>
-      <c r="E47" s="7">
+      <c r="D47">
+        <v>2024</v>
+      </c>
+      <c r="E47" s="1">
         <v>658911.33699999994</v>
       </c>
     </row>
-    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
         <v>5</v>
       </c>
-      <c r="C48" s="6">
+      <c r="C48">
         <v>11</v>
       </c>
-      <c r="D48" s="6">
-        <v>2024</v>
-      </c>
-      <c r="E48" s="7">
+      <c r="D48">
+        <v>2024</v>
+      </c>
+      <c r="E48" s="1">
         <v>697444.65149999992</v>
       </c>
     </row>
-    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
         <v>5</v>
       </c>
-      <c r="C49" s="6">
+      <c r="C49">
         <v>12</v>
       </c>
-      <c r="D49" s="6">
-        <v>2024</v>
-      </c>
-      <c r="E49" s="7">
+      <c r="D49">
+        <v>2024</v>
+      </c>
+      <c r="E49" s="1">
         <v>837874.02649999992</v>
       </c>
     </row>
@@ -1293,13 +1266,13 @@
       <c r="B50" t="s">
         <v>2</v>
       </c>
-      <c r="C50" s="3">
+      <c r="C50">
         <v>1</v>
       </c>
-      <c r="D50" s="3">
-        <v>2025</v>
-      </c>
-      <c r="E50" s="2">
+      <c r="D50">
+        <v>2025</v>
+      </c>
+      <c r="E50" s="1">
         <v>546467.35</v>
       </c>
     </row>
@@ -1310,13 +1283,13 @@
       <c r="B51" t="s">
         <v>2</v>
       </c>
-      <c r="C51" s="3">
-        <v>2</v>
-      </c>
-      <c r="D51" s="3">
-        <v>2025</v>
-      </c>
-      <c r="E51" s="2">
+      <c r="C51">
+        <v>2</v>
+      </c>
+      <c r="D51">
+        <v>2025</v>
+      </c>
+      <c r="E51" s="1">
         <v>648087.1</v>
       </c>
     </row>
@@ -1327,13 +1300,13 @@
       <c r="B52" t="s">
         <v>2</v>
       </c>
-      <c r="C52" s="3">
-        <v>3</v>
-      </c>
-      <c r="D52" s="3">
-        <v>2025</v>
-      </c>
-      <c r="E52" s="2">
+      <c r="C52">
+        <v>3</v>
+      </c>
+      <c r="D52">
+        <v>2025</v>
+      </c>
+      <c r="E52" s="1">
         <v>741740.8</v>
       </c>
     </row>
@@ -1344,13 +1317,13 @@
       <c r="B53" t="s">
         <v>2</v>
       </c>
-      <c r="C53" s="3">
-        <v>4</v>
-      </c>
-      <c r="D53" s="3">
-        <v>2025</v>
-      </c>
-      <c r="E53" s="2">
+      <c r="C53">
+        <v>4</v>
+      </c>
+      <c r="D53">
+        <v>2025</v>
+      </c>
+      <c r="E53" s="1">
         <v>607427.69999999995</v>
       </c>
     </row>
@@ -1361,13 +1334,13 @@
       <c r="B54" t="s">
         <v>2</v>
       </c>
-      <c r="C54" s="3">
-        <v>5</v>
-      </c>
-      <c r="D54" s="3">
-        <v>2025</v>
-      </c>
-      <c r="E54" s="2">
+      <c r="C54">
+        <v>5</v>
+      </c>
+      <c r="D54">
+        <v>2025</v>
+      </c>
+      <c r="E54" s="1">
         <v>640505.15</v>
       </c>
     </row>
@@ -1378,13 +1351,13 @@
       <c r="B55" t="s">
         <v>2</v>
       </c>
-      <c r="C55" s="3">
+      <c r="C55">
         <v>6</v>
       </c>
-      <c r="D55" s="3">
-        <v>2025</v>
-      </c>
-      <c r="E55" s="2">
+      <c r="D55">
+        <v>2025</v>
+      </c>
+      <c r="E55" s="1">
         <v>720247.3</v>
       </c>
     </row>
@@ -1395,13 +1368,13 @@
       <c r="B56" t="s">
         <v>2</v>
       </c>
-      <c r="C56">
+      <c r="C56" s="2">
         <v>7</v>
       </c>
-      <c r="D56">
-        <v>2025</v>
-      </c>
-      <c r="E56" s="1">
+      <c r="D56" s="2">
+        <v>2025</v>
+      </c>
+      <c r="E56" s="3">
         <v>519238.50000000006</v>
       </c>
     </row>
@@ -1412,13 +1385,13 @@
       <c r="B57" t="s">
         <v>2</v>
       </c>
-      <c r="C57">
+      <c r="C57" s="2">
         <v>8</v>
       </c>
-      <c r="D57">
-        <v>2025</v>
-      </c>
-      <c r="E57" s="1">
+      <c r="D57" s="2">
+        <v>2025</v>
+      </c>
+      <c r="E57" s="3">
         <v>581947.30000000005</v>
       </c>
     </row>
@@ -1429,13 +1402,13 @@
       <c r="B58" t="s">
         <v>2</v>
       </c>
-      <c r="C58">
+      <c r="C58" s="2">
         <v>9</v>
       </c>
-      <c r="D58">
-        <v>2025</v>
-      </c>
-      <c r="E58" s="1">
+      <c r="D58" s="2">
+        <v>2025</v>
+      </c>
+      <c r="E58" s="3">
         <v>501345.9</v>
       </c>
     </row>
@@ -1446,13 +1419,13 @@
       <c r="B59" t="s">
         <v>2</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="2">
         <v>10</v>
       </c>
-      <c r="D59">
-        <v>2025</v>
-      </c>
-      <c r="E59" s="1">
+      <c r="D59" s="2">
+        <v>2025</v>
+      </c>
+      <c r="E59" s="3">
         <v>515915.4</v>
       </c>
     </row>
@@ -1463,13 +1436,13 @@
       <c r="B60" t="s">
         <v>2</v>
       </c>
-      <c r="C60">
+      <c r="C60" s="2">
         <v>11</v>
       </c>
-      <c r="D60">
-        <v>2025</v>
-      </c>
-      <c r="E60" s="1">
+      <c r="D60" s="2">
+        <v>2025</v>
+      </c>
+      <c r="E60" s="3">
         <v>659208</v>
       </c>
     </row>
@@ -1480,13 +1453,13 @@
       <c r="B61" t="s">
         <v>2</v>
       </c>
-      <c r="C61">
+      <c r="C61" s="2">
         <v>12</v>
       </c>
-      <c r="D61">
-        <v>2025</v>
-      </c>
-      <c r="E61" s="1">
+      <c r="D61" s="2">
+        <v>2025</v>
+      </c>
+      <c r="E61" s="3">
         <v>441136.30000000005</v>
       </c>
     </row>
@@ -1497,13 +1470,13 @@
       <c r="B62" t="s">
         <v>3</v>
       </c>
-      <c r="C62" s="3">
+      <c r="C62">
         <v>1</v>
       </c>
-      <c r="D62" s="3">
-        <v>2025</v>
-      </c>
-      <c r="E62" s="2">
+      <c r="D62">
+        <v>2025</v>
+      </c>
+      <c r="E62" s="1">
         <v>460018.4</v>
       </c>
     </row>
@@ -1514,13 +1487,13 @@
       <c r="B63" t="s">
         <v>3</v>
       </c>
-      <c r="C63" s="3">
-        <v>2</v>
-      </c>
-      <c r="D63" s="3">
-        <v>2025</v>
-      </c>
-      <c r="E63" s="2">
+      <c r="C63">
+        <v>2</v>
+      </c>
+      <c r="D63">
+        <v>2025</v>
+      </c>
+      <c r="E63" s="1">
         <v>701240.1</v>
       </c>
     </row>
@@ -1531,13 +1504,13 @@
       <c r="B64" t="s">
         <v>3</v>
       </c>
-      <c r="C64" s="3">
-        <v>3</v>
-      </c>
-      <c r="D64" s="3">
-        <v>2025</v>
-      </c>
-      <c r="E64" s="2">
+      <c r="C64">
+        <v>3</v>
+      </c>
+      <c r="D64">
+        <v>2025</v>
+      </c>
+      <c r="E64" s="1">
         <v>761615.1</v>
       </c>
     </row>
@@ -1548,13 +1521,13 @@
       <c r="B65" t="s">
         <v>3</v>
       </c>
-      <c r="C65" s="3">
-        <v>4</v>
-      </c>
-      <c r="D65" s="3">
-        <v>2025</v>
-      </c>
-      <c r="E65" s="2">
+      <c r="C65">
+        <v>4</v>
+      </c>
+      <c r="D65">
+        <v>2025</v>
+      </c>
+      <c r="E65" s="1">
         <v>562320.1</v>
       </c>
     </row>
@@ -1565,13 +1538,13 @@
       <c r="B66" t="s">
         <v>3</v>
       </c>
-      <c r="C66" s="3">
-        <v>5</v>
-      </c>
-      <c r="D66" s="3">
-        <v>2025</v>
-      </c>
-      <c r="E66" s="2">
+      <c r="C66">
+        <v>5</v>
+      </c>
+      <c r="D66">
+        <v>2025</v>
+      </c>
+      <c r="E66" s="1">
         <v>729120.7</v>
       </c>
     </row>
@@ -1582,13 +1555,13 @@
       <c r="B67" t="s">
         <v>3</v>
       </c>
-      <c r="C67" s="3">
+      <c r="C67">
         <v>6</v>
       </c>
-      <c r="D67" s="3">
-        <v>2025</v>
-      </c>
-      <c r="E67" s="2">
+      <c r="D67">
+        <v>2025</v>
+      </c>
+      <c r="E67" s="1">
         <v>872906.35</v>
       </c>
     </row>
@@ -1599,13 +1572,13 @@
       <c r="B68" t="s">
         <v>3</v>
       </c>
-      <c r="C68">
+      <c r="C68" s="2">
         <v>7</v>
       </c>
-      <c r="D68">
-        <v>2025</v>
-      </c>
-      <c r="E68" s="1">
+      <c r="D68" s="2">
+        <v>2025</v>
+      </c>
+      <c r="E68" s="3">
         <v>623986</v>
       </c>
     </row>
@@ -1616,13 +1589,13 @@
       <c r="B69" t="s">
         <v>3</v>
       </c>
-      <c r="C69">
+      <c r="C69" s="2">
         <v>8</v>
       </c>
-      <c r="D69">
-        <v>2025</v>
-      </c>
-      <c r="E69" s="1">
+      <c r="D69" s="2">
+        <v>2025</v>
+      </c>
+      <c r="E69" s="3">
         <v>831565.9</v>
       </c>
     </row>
@@ -1633,13 +1606,13 @@
       <c r="B70" t="s">
         <v>3</v>
       </c>
-      <c r="C70">
+      <c r="C70" s="2">
         <v>9</v>
       </c>
-      <c r="D70">
-        <v>2025</v>
-      </c>
-      <c r="E70" s="1">
+      <c r="D70" s="2">
+        <v>2025</v>
+      </c>
+      <c r="E70" s="3">
         <v>857622.70000000007</v>
       </c>
     </row>
@@ -1650,13 +1623,13 @@
       <c r="B71" t="s">
         <v>3</v>
       </c>
-      <c r="C71">
+      <c r="C71" s="2">
         <v>10</v>
       </c>
-      <c r="D71">
-        <v>2025</v>
-      </c>
-      <c r="E71" s="1">
+      <c r="D71" s="2">
+        <v>2025</v>
+      </c>
+      <c r="E71" s="3">
         <v>635996.9</v>
       </c>
     </row>
@@ -1667,13 +1640,13 @@
       <c r="B72" t="s">
         <v>3</v>
       </c>
-      <c r="C72">
+      <c r="C72" s="2">
         <v>11</v>
       </c>
-      <c r="D72">
-        <v>2025</v>
-      </c>
-      <c r="E72" s="1">
+      <c r="D72" s="2">
+        <v>2025</v>
+      </c>
+      <c r="E72" s="3">
         <v>822134.50000000012</v>
       </c>
     </row>
@@ -1684,13 +1657,13 @@
       <c r="B73" t="s">
         <v>3</v>
       </c>
-      <c r="C73">
+      <c r="C73" s="2">
         <v>12</v>
       </c>
-      <c r="D73">
-        <v>2025</v>
-      </c>
-      <c r="E73" s="1">
+      <c r="D73" s="2">
+        <v>2025</v>
+      </c>
+      <c r="E73" s="3">
         <v>661690.70000000007</v>
       </c>
     </row>
@@ -1701,13 +1674,13 @@
       <c r="B74" t="s">
         <v>4</v>
       </c>
-      <c r="C74" s="3">
+      <c r="C74">
         <v>1</v>
       </c>
-      <c r="D74" s="3">
-        <v>2025</v>
-      </c>
-      <c r="E74" s="2">
+      <c r="D74">
+        <v>2025</v>
+      </c>
+      <c r="E74" s="1">
         <v>483127.65</v>
       </c>
     </row>
@@ -1718,13 +1691,13 @@
       <c r="B75" t="s">
         <v>4</v>
       </c>
-      <c r="C75" s="3">
-        <v>2</v>
-      </c>
-      <c r="D75" s="3">
-        <v>2025</v>
-      </c>
-      <c r="E75" s="2">
+      <c r="C75">
+        <v>2</v>
+      </c>
+      <c r="D75">
+        <v>2025</v>
+      </c>
+      <c r="E75" s="1">
         <v>707742.2</v>
       </c>
     </row>
@@ -1735,13 +1708,13 @@
       <c r="B76" t="s">
         <v>4</v>
       </c>
-      <c r="C76" s="3">
-        <v>3</v>
-      </c>
-      <c r="D76" s="3">
-        <v>2025</v>
-      </c>
-      <c r="E76" s="2">
+      <c r="C76">
+        <v>3</v>
+      </c>
+      <c r="D76">
+        <v>2025</v>
+      </c>
+      <c r="E76" s="1">
         <v>924192.9</v>
       </c>
     </row>
@@ -1752,13 +1725,13 @@
       <c r="B77" t="s">
         <v>4</v>
       </c>
-      <c r="C77" s="3">
-        <v>4</v>
-      </c>
-      <c r="D77" s="3">
-        <v>2025</v>
-      </c>
-      <c r="E77" s="2">
+      <c r="C77">
+        <v>4</v>
+      </c>
+      <c r="D77">
+        <v>2025</v>
+      </c>
+      <c r="E77" s="1">
         <v>648338.94999999995</v>
       </c>
     </row>
@@ -1769,13 +1742,13 @@
       <c r="B78" t="s">
         <v>4</v>
       </c>
-      <c r="C78" s="3">
-        <v>5</v>
-      </c>
-      <c r="D78" s="3">
-        <v>2025</v>
-      </c>
-      <c r="E78" s="2">
+      <c r="C78">
+        <v>5</v>
+      </c>
+      <c r="D78">
+        <v>2025</v>
+      </c>
+      <c r="E78" s="1">
         <v>709702.95</v>
       </c>
     </row>
@@ -1786,13 +1759,13 @@
       <c r="B79" t="s">
         <v>4</v>
       </c>
-      <c r="C79" s="3">
+      <c r="C79">
         <v>6</v>
       </c>
-      <c r="D79" s="3">
-        <v>2025</v>
-      </c>
-      <c r="E79" s="2">
+      <c r="D79">
+        <v>2025</v>
+      </c>
+      <c r="E79" s="1">
         <v>819977.6</v>
       </c>
     </row>
@@ -1803,13 +1776,13 @@
       <c r="B80" t="s">
         <v>4</v>
       </c>
-      <c r="C80">
+      <c r="C80" s="2">
         <v>7</v>
       </c>
-      <c r="D80">
-        <v>2025</v>
-      </c>
-      <c r="E80" s="1">
+      <c r="D80" s="2">
+        <v>2025</v>
+      </c>
+      <c r="E80" s="3">
         <v>600272.20000000007</v>
       </c>
     </row>
@@ -1820,13 +1793,13 @@
       <c r="B81" t="s">
         <v>4</v>
       </c>
-      <c r="C81">
+      <c r="C81" s="2">
         <v>8</v>
       </c>
-      <c r="D81">
-        <v>2025</v>
-      </c>
-      <c r="E81" s="1">
+      <c r="D81" s="2">
+        <v>2025</v>
+      </c>
+      <c r="E81" s="3">
         <v>796998.4</v>
       </c>
     </row>
@@ -1837,13 +1810,13 @@
       <c r="B82" t="s">
         <v>4</v>
       </c>
-      <c r="C82">
+      <c r="C82" s="2">
         <v>9</v>
       </c>
-      <c r="D82">
-        <v>2025</v>
-      </c>
-      <c r="E82" s="1">
+      <c r="D82" s="2">
+        <v>2025</v>
+      </c>
+      <c r="E82" s="3">
         <v>626132.10000000009</v>
       </c>
     </row>
@@ -1854,13 +1827,13 @@
       <c r="B83" t="s">
         <v>4</v>
       </c>
-      <c r="C83">
+      <c r="C83" s="2">
         <v>10</v>
       </c>
-      <c r="D83">
-        <v>2025</v>
-      </c>
-      <c r="E83" s="1">
+      <c r="D83" s="2">
+        <v>2025</v>
+      </c>
+      <c r="E83" s="3">
         <v>591717.5</v>
       </c>
     </row>
@@ -1871,13 +1844,13 @@
       <c r="B84" t="s">
         <v>4</v>
       </c>
-      <c r="C84">
+      <c r="C84" s="2">
         <v>11</v>
       </c>
-      <c r="D84">
-        <v>2025</v>
-      </c>
-      <c r="E84" s="1">
+      <c r="D84" s="2">
+        <v>2025</v>
+      </c>
+      <c r="E84" s="3">
         <v>791032.00000000012</v>
       </c>
     </row>
@@ -1888,13 +1861,13 @@
       <c r="B85" t="s">
         <v>4</v>
       </c>
-      <c r="C85">
+      <c r="C85" s="2">
         <v>12</v>
       </c>
-      <c r="D85">
-        <v>2025</v>
-      </c>
-      <c r="E85" s="1">
+      <c r="D85" s="2">
+        <v>2025</v>
+      </c>
+      <c r="E85" s="3">
         <v>661831.5</v>
       </c>
     </row>
@@ -1905,13 +1878,13 @@
       <c r="B86" t="s">
         <v>5</v>
       </c>
-      <c r="C86" s="3">
+      <c r="C86">
         <v>1</v>
       </c>
-      <c r="D86" s="3">
-        <v>2025</v>
-      </c>
-      <c r="E86" s="2">
+      <c r="D86">
+        <v>2025</v>
+      </c>
+      <c r="E86" s="1">
         <v>444077.1</v>
       </c>
     </row>
@@ -1922,13 +1895,13 @@
       <c r="B87" t="s">
         <v>5</v>
       </c>
-      <c r="C87" s="3">
-        <v>2</v>
-      </c>
-      <c r="D87" s="3">
-        <v>2025</v>
-      </c>
-      <c r="E87" s="2">
+      <c r="C87">
+        <v>2</v>
+      </c>
+      <c r="D87">
+        <v>2025</v>
+      </c>
+      <c r="E87" s="1">
         <v>565701.1</v>
       </c>
     </row>
@@ -1939,13 +1912,13 @@
       <c r="B88" t="s">
         <v>5</v>
       </c>
-      <c r="C88" s="3">
-        <v>3</v>
-      </c>
-      <c r="D88" s="3">
-        <v>2025</v>
-      </c>
-      <c r="E88" s="2">
+      <c r="C88">
+        <v>3</v>
+      </c>
+      <c r="D88">
+        <v>2025</v>
+      </c>
+      <c r="E88" s="1">
         <v>699833.65</v>
       </c>
     </row>
@@ -1956,13 +1929,13 @@
       <c r="B89" t="s">
         <v>5</v>
       </c>
-      <c r="C89" s="3">
-        <v>4</v>
-      </c>
-      <c r="D89" s="3">
-        <v>2025</v>
-      </c>
-      <c r="E89" s="2">
+      <c r="C89">
+        <v>4</v>
+      </c>
+      <c r="D89">
+        <v>2025</v>
+      </c>
+      <c r="E89" s="1">
         <v>578230.35</v>
       </c>
     </row>
@@ -1973,13 +1946,13 @@
       <c r="B90" t="s">
         <v>5</v>
       </c>
-      <c r="C90" s="3">
-        <v>5</v>
-      </c>
-      <c r="D90" s="3">
-        <v>2025</v>
-      </c>
-      <c r="E90" s="2">
+      <c r="C90">
+        <v>5</v>
+      </c>
+      <c r="D90">
+        <v>2025</v>
+      </c>
+      <c r="E90" s="1">
         <v>649040.44999999995</v>
       </c>
     </row>
@@ -1990,13 +1963,13 @@
       <c r="B91" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="3">
+      <c r="C91">
         <v>6</v>
       </c>
-      <c r="D91" s="3">
-        <v>2025</v>
-      </c>
-      <c r="E91" s="2">
+      <c r="D91">
+        <v>2025</v>
+      </c>
+      <c r="E91" s="1">
         <v>737522.6</v>
       </c>
     </row>
@@ -2007,13 +1980,13 @@
       <c r="B92" t="s">
         <v>5</v>
       </c>
-      <c r="C92">
+      <c r="C92" s="2">
         <v>7</v>
       </c>
-      <c r="D92">
-        <v>2025</v>
-      </c>
-      <c r="E92" s="1">
+      <c r="D92" s="2">
+        <v>2025</v>
+      </c>
+      <c r="E92" s="3">
         <v>562719.30000000005</v>
       </c>
     </row>
@@ -2024,13 +1997,13 @@
       <c r="B93" t="s">
         <v>5</v>
       </c>
-      <c r="C93">
+      <c r="C93" s="2">
         <v>8</v>
       </c>
-      <c r="D93">
-        <v>2025</v>
-      </c>
-      <c r="E93" s="1">
+      <c r="D93" s="2">
+        <v>2025</v>
+      </c>
+      <c r="E93" s="3">
         <v>780060.60000000009</v>
       </c>
     </row>
@@ -2041,13 +2014,13 @@
       <c r="B94" t="s">
         <v>5</v>
       </c>
-      <c r="C94">
+      <c r="C94" s="2">
         <v>9</v>
       </c>
-      <c r="D94">
-        <v>2025</v>
-      </c>
-      <c r="E94" s="1">
+      <c r="D94" s="2">
+        <v>2025</v>
+      </c>
+      <c r="E94" s="3">
         <v>606140.70000000007</v>
       </c>
     </row>
@@ -2058,13 +2031,13 @@
       <c r="B95" t="s">
         <v>5</v>
       </c>
-      <c r="C95">
+      <c r="C95" s="2">
         <v>10</v>
       </c>
-      <c r="D95">
-        <v>2025</v>
-      </c>
-      <c r="E95" s="1">
+      <c r="D95" s="2">
+        <v>2025</v>
+      </c>
+      <c r="E95" s="3">
         <v>603181.70000000007</v>
       </c>
     </row>
@@ -2075,13 +2048,13 @@
       <c r="B96" t="s">
         <v>5</v>
       </c>
-      <c r="C96">
+      <c r="C96" s="2">
         <v>11</v>
       </c>
-      <c r="D96">
-        <v>2025</v>
-      </c>
-      <c r="E96" s="1">
+      <c r="D96" s="2">
+        <v>2025</v>
+      </c>
+      <c r="E96" s="3">
         <v>708184.4</v>
       </c>
     </row>
@@ -2092,13 +2065,13 @@
       <c r="B97" t="s">
         <v>5</v>
       </c>
-      <c r="C97">
+      <c r="C97" s="2">
         <v>12</v>
       </c>
-      <c r="D97">
-        <v>2025</v>
-      </c>
-      <c r="E97" s="1">
+      <c r="D97" s="2">
+        <v>2025</v>
+      </c>
+      <c r="E97" s="3">
         <v>721743.00000000012</v>
       </c>
     </row>
@@ -2109,13 +2082,13 @@
       <c r="B98" t="s">
         <v>2</v>
       </c>
-      <c r="C98">
+      <c r="C98" s="2">
         <v>1</v>
       </c>
-      <c r="D98">
+      <c r="D98" s="2">
         <v>2026</v>
       </c>
-      <c r="E98" s="1">
+      <c r="E98" s="3">
         <v>447132.4</v>
       </c>
     </row>
@@ -2126,13 +2099,13 @@
       <c r="B99" t="s">
         <v>2</v>
       </c>
-      <c r="C99">
-        <v>2</v>
-      </c>
-      <c r="D99">
+      <c r="C99" s="2">
+        <v>2</v>
+      </c>
+      <c r="D99" s="2">
         <v>2026</v>
       </c>
-      <c r="E99" s="1">
+      <c r="E99" s="3">
         <v>583671</v>
       </c>
     </row>
@@ -2143,13 +2116,13 @@
       <c r="B100" t="s">
         <v>2</v>
       </c>
-      <c r="C100">
-        <v>3</v>
-      </c>
-      <c r="D100">
+      <c r="C100" s="2">
+        <v>3</v>
+      </c>
+      <c r="D100" s="2">
         <v>2026</v>
       </c>
-      <c r="E100" s="1">
+      <c r="E100" s="3">
         <v>543246</v>
       </c>
     </row>
@@ -2160,13 +2133,13 @@
       <c r="B101" t="s">
         <v>2</v>
       </c>
-      <c r="C101">
-        <v>4</v>
-      </c>
-      <c r="D101">
+      <c r="C101" s="2">
+        <v>4</v>
+      </c>
+      <c r="D101" s="2">
         <v>2026</v>
       </c>
-      <c r="E101" s="1">
+      <c r="E101" s="3">
         <v>420537.7</v>
       </c>
     </row>
@@ -2177,13 +2150,13 @@
       <c r="B102" t="s">
         <v>2</v>
       </c>
-      <c r="C102">
-        <v>5</v>
-      </c>
-      <c r="D102">
+      <c r="C102" s="2">
+        <v>5</v>
+      </c>
+      <c r="D102" s="2">
         <v>2026</v>
       </c>
-      <c r="E102" s="1">
+      <c r="E102" s="3">
         <v>610426.30000000005</v>
       </c>
     </row>
@@ -2194,13 +2167,13 @@
       <c r="B103" t="s">
         <v>2</v>
       </c>
-      <c r="C103">
+      <c r="C103" s="2">
         <v>6</v>
       </c>
-      <c r="D103">
+      <c r="D103" s="2">
         <v>2026</v>
       </c>
-      <c r="E103" s="1">
+      <c r="E103" s="3">
         <v>430988.80000000005</v>
       </c>
     </row>
@@ -2211,13 +2184,13 @@
       <c r="B104" t="s">
         <v>3</v>
       </c>
-      <c r="C104">
+      <c r="C104" s="2">
         <v>1</v>
       </c>
-      <c r="D104">
+      <c r="D104" s="2">
         <v>2026</v>
       </c>
-      <c r="E104" s="1">
+      <c r="E104" s="3">
         <v>468160.00000000006</v>
       </c>
     </row>
@@ -2228,13 +2201,13 @@
       <c r="B105" t="s">
         <v>3</v>
       </c>
-      <c r="C105">
-        <v>2</v>
-      </c>
-      <c r="D105">
+      <c r="C105" s="2">
+        <v>2</v>
+      </c>
+      <c r="D105" s="2">
         <v>2026</v>
       </c>
-      <c r="E105" s="1">
+      <c r="E105" s="3">
         <v>710494.4</v>
       </c>
     </row>
@@ -2245,13 +2218,13 @@
       <c r="B106" t="s">
         <v>3</v>
       </c>
-      <c r="C106">
-        <v>3</v>
-      </c>
-      <c r="D106">
+      <c r="C106" s="2">
+        <v>3</v>
+      </c>
+      <c r="D106" s="2">
         <v>2026</v>
       </c>
-      <c r="E106" s="1">
+      <c r="E106" s="3">
         <v>734202.70000000007</v>
       </c>
     </row>
@@ -2262,13 +2235,13 @@
       <c r="B107" t="s">
         <v>3</v>
       </c>
-      <c r="C107">
-        <v>4</v>
-      </c>
-      <c r="D107">
+      <c r="C107" s="2">
+        <v>4</v>
+      </c>
+      <c r="D107" s="2">
         <v>2026</v>
       </c>
-      <c r="E107" s="1">
+      <c r="E107" s="3">
         <v>533989.5</v>
       </c>
     </row>
@@ -2279,13 +2252,13 @@
       <c r="B108" t="s">
         <v>3</v>
       </c>
-      <c r="C108">
-        <v>5</v>
-      </c>
-      <c r="D108">
+      <c r="C108" s="2">
+        <v>5</v>
+      </c>
+      <c r="D108" s="2">
         <v>2026</v>
       </c>
-      <c r="E108" s="1">
+      <c r="E108" s="3">
         <v>783138.4</v>
       </c>
     </row>
@@ -2296,13 +2269,13 @@
       <c r="B109" t="s">
         <v>3</v>
       </c>
-      <c r="C109">
+      <c r="C109" s="2">
         <v>6</v>
       </c>
-      <c r="D109">
+      <c r="D109" s="2">
         <v>2026</v>
       </c>
-      <c r="E109" s="1">
+      <c r="E109" s="3">
         <v>632283.30000000005</v>
       </c>
     </row>
@@ -2313,13 +2286,13 @@
       <c r="B110" t="s">
         <v>4</v>
       </c>
-      <c r="C110">
+      <c r="C110" s="2">
         <v>1</v>
       </c>
-      <c r="D110">
+      <c r="D110" s="2">
         <v>2026</v>
       </c>
-      <c r="E110" s="1">
+      <c r="E110" s="3">
         <v>420468.4</v>
       </c>
     </row>
@@ -2330,13 +2303,13 @@
       <c r="B111" t="s">
         <v>4</v>
       </c>
-      <c r="C111">
-        <v>2</v>
-      </c>
-      <c r="D111">
+      <c r="C111" s="2">
+        <v>2</v>
+      </c>
+      <c r="D111" s="2">
         <v>2026</v>
       </c>
-      <c r="E111" s="1">
+      <c r="E111" s="3">
         <v>768489.70000000007</v>
       </c>
     </row>
@@ -2347,13 +2320,13 @@
       <c r="B112" t="s">
         <v>4</v>
       </c>
-      <c r="C112">
-        <v>3</v>
-      </c>
-      <c r="D112">
+      <c r="C112" s="2">
+        <v>3</v>
+      </c>
+      <c r="D112" s="2">
         <v>2026</v>
       </c>
-      <c r="E112" s="1">
+      <c r="E112" s="3">
         <v>707430.9</v>
       </c>
     </row>
@@ -2364,13 +2337,13 @@
       <c r="B113" t="s">
         <v>4</v>
       </c>
-      <c r="C113">
-        <v>4</v>
-      </c>
-      <c r="D113">
+      <c r="C113" s="2">
+        <v>4</v>
+      </c>
+      <c r="D113" s="2">
         <v>2026</v>
       </c>
-      <c r="E113" s="1">
+      <c r="E113" s="3">
         <v>548621.70000000007</v>
       </c>
     </row>
@@ -2381,13 +2354,13 @@
       <c r="B114" t="s">
         <v>4</v>
       </c>
-      <c r="C114">
-        <v>5</v>
-      </c>
-      <c r="D114">
+      <c r="C114" s="2">
+        <v>5</v>
+      </c>
+      <c r="D114" s="2">
         <v>2026</v>
       </c>
-      <c r="E114" s="1">
+      <c r="E114" s="3">
         <v>628012</v>
       </c>
     </row>
@@ -2398,13 +2371,13 @@
       <c r="B115" t="s">
         <v>4</v>
       </c>
-      <c r="C115">
+      <c r="C115" s="2">
         <v>6</v>
       </c>
-      <c r="D115">
+      <c r="D115" s="2">
         <v>2026</v>
       </c>
-      <c r="E115" s="1">
+      <c r="E115" s="3">
         <v>654494.5</v>
       </c>
     </row>
@@ -2415,13 +2388,13 @@
       <c r="B116" t="s">
         <v>5</v>
       </c>
-      <c r="C116">
+      <c r="C116" s="2">
         <v>1</v>
       </c>
-      <c r="D116">
+      <c r="D116" s="2">
         <v>2026</v>
       </c>
-      <c r="E116" s="1">
+      <c r="E116" s="3">
         <v>408622.50000000006</v>
       </c>
     </row>
@@ -2432,13 +2405,13 @@
       <c r="B117" t="s">
         <v>5</v>
       </c>
-      <c r="C117">
-        <v>2</v>
-      </c>
-      <c r="D117">
+      <c r="C117" s="2">
+        <v>2</v>
+      </c>
+      <c r="D117" s="2">
         <v>2026</v>
       </c>
-      <c r="E117" s="1">
+      <c r="E117" s="3">
         <v>710213.9</v>
       </c>
     </row>
@@ -2449,13 +2422,13 @@
       <c r="B118" t="s">
         <v>5</v>
       </c>
-      <c r="C118">
-        <v>3</v>
-      </c>
-      <c r="D118">
+      <c r="C118" s="2">
+        <v>3</v>
+      </c>
+      <c r="D118" s="2">
         <v>2026</v>
       </c>
-      <c r="E118" s="1">
+      <c r="E118" s="3">
         <v>534640.70000000007</v>
       </c>
     </row>
@@ -2466,13 +2439,13 @@
       <c r="B119" t="s">
         <v>5</v>
       </c>
-      <c r="C119">
-        <v>4</v>
-      </c>
-      <c r="D119">
+      <c r="C119" s="2">
+        <v>4</v>
+      </c>
+      <c r="D119" s="2">
         <v>2026</v>
       </c>
-      <c r="E119" s="1">
+      <c r="E119" s="3">
         <v>565877.4</v>
       </c>
     </row>
@@ -2483,13 +2456,13 @@
       <c r="B120" t="s">
         <v>5</v>
       </c>
-      <c r="C120">
-        <v>5</v>
-      </c>
-      <c r="D120">
+      <c r="C120" s="2">
+        <v>5</v>
+      </c>
+      <c r="D120" s="2">
         <v>2026</v>
       </c>
-      <c r="E120" s="1">
+      <c r="E120" s="3">
         <v>699802.4</v>
       </c>
     </row>
@@ -2500,13 +2473,13 @@
       <c r="B121" t="s">
         <v>5</v>
       </c>
-      <c r="C121">
+      <c r="C121" s="2">
         <v>6</v>
       </c>
-      <c r="D121">
+      <c r="D121" s="2">
         <v>2026</v>
       </c>
-      <c r="E121" s="1">
+      <c r="E121" s="3">
         <v>649240.9</v>
       </c>
     </row>
